--- a/public/plantillas/Makro/offer_template FR.xlsx
+++ b/public/plantillas/Makro/offer_template FR.xlsx
@@ -1477,25 +1477,404 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G22" s="4"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641312</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>108.33</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>106</v>
+      </c>
+      <c r="O22">
+        <v>104</v>
+      </c>
+      <c r="P22">
+        <v>102</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="V22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G23" s="4"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641336</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>108.33</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>106</v>
+      </c>
+      <c r="O23">
+        <v>104</v>
+      </c>
+      <c r="P23">
+        <v>102</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="V23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641329</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>108.33</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>106</v>
+      </c>
+      <c r="O24">
+        <v>104</v>
+      </c>
+      <c r="P24">
+        <v>102</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="V24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G25" s="3"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641343</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>108.33</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>106</v>
+      </c>
+      <c r="O25">
+        <v>104</v>
+      </c>
+      <c r="P25">
+        <v>102</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="V25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G26" s="3"/>
+      <c r="A26" s="2">
+        <v>8437027641350</v>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>145</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>143</v>
+      </c>
+      <c r="O26">
+        <v>141</v>
+      </c>
+      <c r="P26">
+        <v>139</v>
+      </c>
+      <c r="Q26">
+        <v>137</v>
+      </c>
+      <c r="V26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G27" s="3"/>
+      <c r="A27" s="2">
+        <v>8437027641374</v>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>145</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>143</v>
+      </c>
+      <c r="O27">
+        <v>141</v>
+      </c>
+      <c r="P27">
+        <v>139</v>
+      </c>
+      <c r="Q27">
+        <v>137</v>
+      </c>
+      <c r="V27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G28" s="3"/>
+      <c r="A28" s="2">
+        <v>8437027641367</v>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>145</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>143</v>
+      </c>
+      <c r="O28">
+        <v>141</v>
+      </c>
+      <c r="P28">
+        <v>139</v>
+      </c>
+      <c r="Q28">
+        <v>137</v>
+      </c>
+      <c r="V28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G29" s="3"/>
+      <c r="A29" s="2">
+        <v>8437027641381</v>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>145</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>143</v>
+      </c>
+      <c r="O29">
+        <v>141</v>
+      </c>
+      <c r="P29">
+        <v>139</v>
+      </c>
+      <c r="Q29">
+        <v>137</v>
+      </c>
+      <c r="V29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="30" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
       <c r="G30" s="3"/>

--- a/public/plantillas/Makro/offer_template FR.xlsx
+++ b/public/plantillas/Makro/offer_template FR.xlsx
@@ -1877,34 +1877,514 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G30" s="3"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641534</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>97</v>
+      </c>
+      <c r="O30">
+        <v>96</v>
+      </c>
+      <c r="P30">
+        <v>95</v>
+      </c>
+      <c r="Q30">
+        <v>94</v>
+      </c>
+      <c r="V30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G31" s="3"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641480</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>99.17</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>96.19</v>
+      </c>
+      <c r="O31">
+        <v>95.2</v>
+      </c>
+      <c r="P31">
+        <v>94.21</v>
+      </c>
+      <c r="Q31">
+        <v>93.22</v>
+      </c>
+      <c r="V31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="32" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G32" s="3"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641497</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>250</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>242.5</v>
+      </c>
+      <c r="O32">
+        <v>240</v>
+      </c>
+      <c r="P32">
+        <v>237.5</v>
+      </c>
+      <c r="Q32">
+        <v>235</v>
+      </c>
+      <c r="V32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G33" s="3"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641442</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>250</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>242.5</v>
+      </c>
+      <c r="O33">
+        <v>240</v>
+      </c>
+      <c r="P33">
+        <v>237.5</v>
+      </c>
+      <c r="Q33">
+        <v>235</v>
+      </c>
+      <c r="V33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G34" s="3"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641503</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>149.17</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>144.69</v>
+      </c>
+      <c r="O34">
+        <v>143.2</v>
+      </c>
+      <c r="P34">
+        <v>141.71</v>
+      </c>
+      <c r="Q34">
+        <v>140.22</v>
+      </c>
+      <c r="V34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G35" s="3"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641459</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>149.17</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>144.69</v>
+      </c>
+      <c r="O35">
+        <v>143.2</v>
+      </c>
+      <c r="P35">
+        <v>141.71</v>
+      </c>
+      <c r="Q35">
+        <v>140.22</v>
+      </c>
+      <c r="V35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G36" s="3"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641510</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>165.83</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>160.86</v>
+      </c>
+      <c r="O36">
+        <v>159.2</v>
+      </c>
+      <c r="P36">
+        <v>157.54</v>
+      </c>
+      <c r="Q36">
+        <v>155.88</v>
+      </c>
+      <c r="V36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G37" s="3"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641466</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>166.67</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>161.67</v>
+      </c>
+      <c r="O37">
+        <v>160</v>
+      </c>
+      <c r="P37">
+        <v>158.34</v>
+      </c>
+      <c r="Q37">
+        <v>156.67</v>
+      </c>
+      <c r="V37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G38" s="3"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641527</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>232.5</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>225.53</v>
+      </c>
+      <c r="O38">
+        <v>223.2</v>
+      </c>
+      <c r="P38">
+        <v>220.88</v>
+      </c>
+      <c r="Q38">
+        <v>218.55</v>
+      </c>
+      <c r="V38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="G39" s="3"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641473</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>232.5</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR_MAIN</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>225.53</v>
+      </c>
+      <c r="O39">
+        <v>223.2</v>
+      </c>
+      <c r="P39">
+        <v>220.88</v>
+      </c>
+      <c r="Q39">
+        <v>218.55</v>
+      </c>
+      <c r="V39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="7:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="G40" s="3"/>
